--- a/Documents/SEIL-country-F2H26-Translation Document.xlsx
+++ b/Documents/SEIL-country-F2H26-Translation Document.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CRM 2.0\Adobe Web Forms\F2H26\SEIL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Adobe-Form-Builder-main\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C4306F-EEA5-4BB1-BCD8-7CF0C59EB794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDB54450-912E-4DCB-981E-CDB0E75C7CBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1710" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Complete Translations" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="213">
   <si>
     <t>Translation</t>
   </si>
@@ -682,6 +682,12 @@
   </si>
   <si>
     <t>https://www.samsung.com/il/offer/ (Please update the redirection link)</t>
+  </si>
+  <si>
+    <t>Project Code</t>
+  </si>
+  <si>
+    <t>F2H26</t>
   </si>
 </sst>
 </file>
@@ -1368,9 +1374,15 @@
     </row>
     <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="16"/>
-      <c r="B2"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
+      <c r="B2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8"/>
